--- a/Contactos Envio Diario.xlsx
+++ b/Contactos Envio Diario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC41\Desktop\Dev\Informe Diario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFA5A29D-8BC5-4B9A-A343-206E0E0DF38E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B825420-FCCD-4E5F-903F-657B28BA76ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,30 +20,28 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
     <t>Correo</t>
   </si>
   <si>
     <t>tbrellenthin@medhesa.es</t>
   </si>
+  <si>
+    <t>esanroman@medhesa.es</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <u/>
@@ -101,18 +99,19 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -122,8 +121,6 @@
   <dxfs count="5">
     <dxf>
       <font>
-        <condense val="0"/>
-        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -166,6 +163,8 @@
     </dxf>
     <dxf>
       <font>
+        <condense val="0"/>
+        <extend val="0"/>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -529,7 +528,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B4:B5"/>
+  <dimension ref="B4:B6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="51" bestFit="1" customWidth="1"/>
@@ -541,28 +540,33 @@
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>1</v>
       </c>
     </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="B1:B1048576">
-    <cfRule type="duplicateValues" dxfId="4" priority="6221"/>
+  <conditionalFormatting sqref="B1:B3 B5:B65190">
+    <cfRule type="duplicateValues" dxfId="4" priority="6233" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1:B3 B5:B1048576">
     <cfRule type="duplicateValues" dxfId="3" priority="6224"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B5:B1048576">
     <cfRule type="duplicateValues" dxfId="2" priority="6227"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B5:B1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="6230"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1:B3 B5:B65190">
-    <cfRule type="duplicateValues" dxfId="0" priority="6233" stopIfTrue="1"/>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="6221"/>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" xr:uid="{1D0E2F23-9CA4-444B-AFA7-414CC66BD409}"/>
+    <hyperlink ref="B5" r:id="rId2" xr:uid="{2A168598-88B0-4640-A4C0-7C23A4A6ACE3}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>